--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -9892,7 +9892,7 @@
         <v>ГОСТ Р ИСО 9001-2015</v>
       </c>
       <c r="F413" t="str">
-        <v/>
+        <v>РФ</v>
       </c>
       <c r="G413">
         <v>47147</v>

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -31976,8 +31976,8 @@
       <c r="F1373" t="str">
         <v>РФ</v>
       </c>
-      <c r="G1373" t="str">
-        <v/>
+      <c r="G1373">
+        <v>47266</v>
       </c>
     </row>
     <row r="1374">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -20569,7 +20569,7 @@
         <v>РФ</v>
       </c>
       <c r="G877">
-        <v>47112</v>
+        <v>47392</v>
       </c>
     </row>
     <row r="878">

--- a/sites/URS/URS_Certifications/URS_Certifications.xlsx
+++ b/sites/URS/URS_Certifications/URS_Certifications.xlsx
@@ -6652,7 +6652,7 @@
         <v>РФ</v>
       </c>
       <c r="G272">
-        <v>46289</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="273">
@@ -6675,7 +6675,7 @@
         <v>РФ</v>
       </c>
       <c r="G273">
-        <v>46289</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="274">
@@ -6698,7 +6698,7 @@
         <v>РФ</v>
       </c>
       <c r="G274">
-        <v>46289</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="275">
@@ -6721,7 +6721,7 @@
         <v>РФ</v>
       </c>
       <c r="G275">
-        <v>46289</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="276">
@@ -6744,7 +6744,7 @@
         <v>РФ</v>
       </c>
       <c r="G276">
-        <v>46289</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="277">
@@ -6767,7 +6767,7 @@
         <v>РФ</v>
       </c>
       <c r="G277">
-        <v>46289</v>
+        <v>47384</v>
       </c>
     </row>
     <row r="278">
@@ -24203,7 +24203,7 @@
         <v>РФ</v>
       </c>
       <c r="G1035">
-        <v>46227</v>
+        <v>46596</v>
       </c>
     </row>
     <row r="1036">
